--- a/data_generation/10_aquatic_toxicity/folpet_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/folpet_aquatic_toxicity.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2920E596-A7A2-4EF1-8FD4-E354ED16F755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CA1032-0076-466E-BECC-92143C0E2457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DCCE98E3-7ECB-464D-B3A9-333AAEFCC845}"/>
   </bookViews>
